--- a/data/events-tb.xlsx
+++ b/data/events-tb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\therules\therules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3987A40-8316-46FF-8770-6952B4979B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE84C3E-5610-46F6-BC5C-E14A8083BDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="2370" windowWidth="24390" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5930" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5981" uniqueCount="31">
   <si>
     <t>Ruthless Slaughter</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>Event-6</t>
+  </si>
+  <si>
+    <t>Event-7</t>
+  </si>
+  <si>
+    <t>Pumpkin Harvest</t>
   </si>
 </sst>
 </file>
@@ -717,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2179"/>
+  <dimension ref="A1:I2179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="10" customWidth="1"/>
@@ -728,9 +734,10 @@
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>27</v>
       </c>
@@ -755,8 +762,11 @@
       <c r="H1" s="27" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>45809</v>
       </c>
@@ -769,7 +779,7 @@
       <c r="D2" s="6"/>
       <c r="E2" s="13"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>45810</v>
       </c>
@@ -786,7 +796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>45811</v>
       </c>
@@ -801,7 +811,7 @@
       </c>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>45812</v>
       </c>
@@ -814,7 +824,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>45813</v>
       </c>
@@ -827,7 +837,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="13"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>45814</v>
       </c>
@@ -840,7 +850,7 @@
       <c r="D7" s="6"/>
       <c r="E7" s="13"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>45815</v>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E8" s="13"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>45816</v>
       </c>
@@ -872,7 +882,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>45817</v>
       </c>
@@ -887,7 +897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>45818</v>
       </c>
@@ -900,7 +910,7 @@
       <c r="D11" s="6"/>
       <c r="E11" s="13"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>45819</v>
       </c>
@@ -913,7 +923,7 @@
       <c r="D12" s="6"/>
       <c r="E12" s="13"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>45820</v>
       </c>
@@ -926,7 +936,7 @@
       <c r="D13" s="6"/>
       <c r="E13" s="13"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>45821</v>
       </c>
@@ -939,7 +949,7 @@
       <c r="D14" s="6"/>
       <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>45822</v>
       </c>
@@ -956,7 +966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>45823</v>
       </c>
@@ -8305,7 +8315,7 @@
       <c r="F496" s="6"/>
       <c r="G496" s="4"/>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" s="10">
         <v>46304</v>
       </c>
@@ -8320,7 +8330,7 @@
       <c r="F497" s="6"/>
       <c r="G497" s="4"/>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" s="10">
         <v>46305</v>
       </c>
@@ -8335,7 +8345,7 @@
       <c r="F498" s="6"/>
       <c r="G498" s="4"/>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" s="10">
         <v>46306</v>
       </c>
@@ -8350,7 +8360,7 @@
       <c r="F499" s="6"/>
       <c r="G499" s="4"/>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" s="10">
         <v>46307</v>
       </c>
@@ -8367,7 +8377,7 @@
       <c r="F500" s="6"/>
       <c r="G500" s="4"/>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" s="10">
         <v>46308</v>
       </c>
@@ -8386,7 +8396,7 @@
       <c r="F501" s="6"/>
       <c r="G501" s="4"/>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" s="10">
         <v>46309</v>
       </c>
@@ -8403,7 +8413,7 @@
       <c r="F502" s="6"/>
       <c r="G502" s="4"/>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" s="10">
         <v>46310</v>
       </c>
@@ -8418,7 +8428,7 @@
       <c r="F503" s="6"/>
       <c r="G503" s="4"/>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" s="10">
         <v>46311</v>
       </c>
@@ -8433,7 +8443,7 @@
       <c r="F504" s="6"/>
       <c r="G504" s="4"/>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" s="10">
         <v>46312</v>
       </c>
@@ -8451,7 +8461,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" s="10">
         <v>46313</v>
       </c>
@@ -8466,7 +8476,7 @@
       <c r="F506" s="6"/>
       <c r="G506" s="4"/>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" s="10">
         <v>46314</v>
       </c>
@@ -8485,7 +8495,7 @@
       <c r="F507" s="6"/>
       <c r="G507" s="4"/>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" s="10">
         <v>46315</v>
       </c>
@@ -8502,7 +8512,7 @@
       <c r="F508" s="6"/>
       <c r="G508" s="4"/>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" s="10">
         <v>46316</v>
       </c>
@@ -8517,7 +8527,7 @@
       <c r="F509" s="6"/>
       <c r="G509" s="4"/>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" s="10">
         <v>46317</v>
       </c>
@@ -8534,7 +8544,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" s="10">
         <v>46318</v>
       </c>
@@ -8548,8 +8558,11 @@
       <c r="E511" s="4"/>
       <c r="F511" s="6"/>
       <c r="G511" s="4"/>
-    </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I511" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" s="10">
         <v>46319</v>
       </c>
@@ -8565,8 +8578,11 @@
       <c r="E512" s="4"/>
       <c r="F512" s="6"/>
       <c r="G512" s="4"/>
-    </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I512" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" s="10">
         <v>46320</v>
       </c>
@@ -8584,8 +8600,11 @@
       </c>
       <c r="F513" s="6"/>
       <c r="G513" s="4"/>
-    </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I513" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" s="10">
         <v>46321</v>
       </c>
@@ -8601,8 +8620,11 @@
       </c>
       <c r="F514" s="6"/>
       <c r="G514" s="4"/>
-    </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I514" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" s="10">
         <v>46322</v>
       </c>
@@ -8616,8 +8638,11 @@
       <c r="E515" s="4"/>
       <c r="F515" s="6"/>
       <c r="G515" s="4"/>
-    </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I515" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" s="10">
         <v>46323</v>
       </c>
@@ -8631,8 +8656,11 @@
       <c r="E516" s="4"/>
       <c r="F516" s="6"/>
       <c r="G516" s="4"/>
-    </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I516" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" s="10">
         <v>46324</v>
       </c>
@@ -8646,8 +8674,11 @@
       <c r="E517" s="4"/>
       <c r="F517" s="6"/>
       <c r="G517" s="4"/>
-    </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I517" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" s="10">
         <v>46325</v>
       </c>
@@ -8664,8 +8695,11 @@
       <c r="H518" s="23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I518" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" s="10">
         <v>46326</v>
       </c>
@@ -8685,8 +8719,11 @@
         <v>20</v>
       </c>
       <c r="G519" s="3"/>
-    </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I519" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" s="10">
         <v>46327</v>
       </c>
@@ -8702,8 +8739,11 @@
       <c r="E520" s="4"/>
       <c r="F520" s="6"/>
       <c r="G520" s="4"/>
-    </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I520" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" s="10">
         <v>46328</v>
       </c>
@@ -8718,7 +8758,7 @@
       <c r="F521" s="6"/>
       <c r="G521" s="4"/>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" s="10">
         <v>46329</v>
       </c>
@@ -8733,7 +8773,7 @@
       <c r="F522" s="6"/>
       <c r="G522" s="4"/>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" s="10">
         <v>46330</v>
       </c>
@@ -8748,7 +8788,7 @@
       <c r="F523" s="6"/>
       <c r="G523" s="4"/>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" s="10">
         <v>46331</v>
       </c>
@@ -8765,7 +8805,7 @@
       <c r="F524" s="6"/>
       <c r="G524" s="4"/>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" s="10">
         <v>46332</v>
       </c>
@@ -8784,7 +8824,7 @@
       <c r="F525" s="6"/>
       <c r="G525" s="4"/>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" s="10">
         <v>46333</v>
       </c>
@@ -8801,7 +8841,7 @@
       <c r="F526" s="6"/>
       <c r="G526" s="4"/>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" s="10">
         <v>46334</v>
       </c>
@@ -8816,7 +8856,7 @@
       <c r="F527" s="6"/>
       <c r="G527" s="4"/>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" s="10">
         <v>46335</v>
       </c>
@@ -14397,7 +14437,7 @@
       <c r="F864" s="6"/>
       <c r="G864" s="4"/>
     </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" s="10">
         <v>46672</v>
       </c>
@@ -14412,7 +14452,7 @@
       <c r="F865" s="6"/>
       <c r="G865" s="4"/>
     </row>
-    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" s="10">
         <v>46673</v>
       </c>
@@ -14427,7 +14467,7 @@
       <c r="F866" s="6"/>
       <c r="G866" s="4"/>
     </row>
-    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" s="10">
         <v>46674</v>
       </c>
@@ -14446,7 +14486,7 @@
       <c r="F867" s="6"/>
       <c r="G867" s="4"/>
     </row>
-    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" s="10">
         <v>46675</v>
       </c>
@@ -14463,7 +14503,7 @@
       <c r="F868" s="6"/>
       <c r="G868" s="4"/>
     </row>
-    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" s="10">
         <v>46676</v>
       </c>
@@ -14481,7 +14521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" s="10">
         <v>46677</v>
       </c>
@@ -14498,7 +14538,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" s="10">
         <v>46678</v>
       </c>
@@ -14513,7 +14553,7 @@
       <c r="F871" s="6"/>
       <c r="G871" s="4"/>
     </row>
-    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" s="10">
         <v>46679</v>
       </c>
@@ -14530,7 +14570,7 @@
       <c r="F872" s="6"/>
       <c r="G872" s="4"/>
     </row>
-    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" s="10">
         <v>46680</v>
       </c>
@@ -14549,7 +14589,7 @@
       <c r="F873" s="6"/>
       <c r="G873" s="4"/>
     </row>
-    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" s="10">
         <v>46681</v>
       </c>
@@ -14566,7 +14606,7 @@
       <c r="F874" s="6"/>
       <c r="G874" s="4"/>
     </row>
-    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" s="10">
         <v>46682</v>
       </c>
@@ -14581,7 +14621,7 @@
       <c r="F875" s="6"/>
       <c r="G875" s="4"/>
     </row>
-    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" s="10">
         <v>46683</v>
       </c>
@@ -14595,8 +14635,11 @@
       <c r="E876" s="4"/>
       <c r="F876" s="6"/>
       <c r="G876" s="4"/>
-    </row>
-    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I876" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" s="10">
         <v>46684</v>
       </c>
@@ -14610,8 +14653,11 @@
       <c r="E877" s="4"/>
       <c r="F877" s="6"/>
       <c r="G877" s="4"/>
-    </row>
-    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I877" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" s="10">
         <v>46685</v>
       </c>
@@ -14625,8 +14671,11 @@
       <c r="E878" s="4"/>
       <c r="F878" s="7"/>
       <c r="G878" s="5"/>
-    </row>
-    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I878" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" s="10">
         <v>46686</v>
       </c>
@@ -14646,8 +14695,11 @@
         <v>20</v>
       </c>
       <c r="G879" s="3"/>
-    </row>
-    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I879" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" s="10">
         <v>46687</v>
       </c>
@@ -14663,8 +14715,11 @@
       <c r="E880" s="4"/>
       <c r="F880" s="6"/>
       <c r="G880" s="4"/>
-    </row>
-    <row r="881" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I880" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" s="10">
         <v>46688</v>
       </c>
@@ -14678,8 +14733,11 @@
       <c r="E881" s="4"/>
       <c r="F881" s="6"/>
       <c r="G881" s="4"/>
-    </row>
-    <row r="882" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I881" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" s="10">
         <v>46689</v>
       </c>
@@ -14696,8 +14754,11 @@
       <c r="H882" s="23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="883" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I882" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" s="10">
         <v>46690</v>
       </c>
@@ -14711,8 +14772,11 @@
       <c r="E883" s="5"/>
       <c r="F883" s="6"/>
       <c r="G883" s="4"/>
-    </row>
-    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I883" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" s="10">
         <v>46691</v>
       </c>
@@ -14728,8 +14792,11 @@
       <c r="E884" s="3"/>
       <c r="F884" s="6"/>
       <c r="G884" s="4"/>
-    </row>
-    <row r="885" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I884" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" s="10">
         <v>46692</v>
       </c>
@@ -14747,8 +14814,11 @@
       </c>
       <c r="F885" s="6"/>
       <c r="G885" s="4"/>
-    </row>
-    <row r="886" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I885" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" s="10">
         <v>46693</v>
       </c>
@@ -14765,7 +14835,7 @@
       <c r="F886" s="6"/>
       <c r="G886" s="4"/>
     </row>
-    <row r="887" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" s="10">
         <v>46694</v>
       </c>
@@ -14780,7 +14850,7 @@
       <c r="F887" s="6"/>
       <c r="G887" s="4"/>
     </row>
-    <row r="888" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" s="10">
         <v>46695</v>
       </c>
@@ -14795,7 +14865,7 @@
       <c r="F888" s="6"/>
       <c r="G888" s="4"/>
     </row>
-    <row r="889" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" s="10">
         <v>46696</v>
       </c>
@@ -14810,7 +14880,7 @@
       <c r="F889" s="6"/>
       <c r="G889" s="4"/>
     </row>
-    <row r="890" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" s="10">
         <v>46697</v>
       </c>
@@ -14825,7 +14895,7 @@
       <c r="F890" s="6"/>
       <c r="G890" s="4"/>
     </row>
-    <row r="891" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" s="10">
         <v>46698</v>
       </c>
@@ -14844,7 +14914,7 @@
       <c r="F891" s="6"/>
       <c r="G891" s="4"/>
     </row>
-    <row r="892" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" s="10">
         <v>46699</v>
       </c>
@@ -14861,7 +14931,7 @@
       <c r="F892" s="6"/>
       <c r="G892" s="4"/>
     </row>
-    <row r="893" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" s="10">
         <v>46700</v>
       </c>
@@ -14876,7 +14946,7 @@
       <c r="F893" s="6"/>
       <c r="G893" s="4"/>
     </row>
-    <row r="894" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" s="10">
         <v>46701</v>
       </c>
@@ -14893,7 +14963,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="895" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" s="10">
         <v>46702</v>
       </c>
@@ -14911,7 +14981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="896" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" s="10">
         <v>46703</v>
       </c>
@@ -20491,7 +20561,7 @@
       <c r="F1232" s="6"/>
       <c r="G1232" s="4"/>
     </row>
-    <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1233" s="10">
         <v>47040</v>
       </c>
@@ -20513,7 +20583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1234" s="10">
         <v>47041</v>
       </c>
@@ -20530,7 +20600,7 @@
       <c r="F1234" s="6"/>
       <c r="G1234" s="4"/>
     </row>
-    <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1235" s="10">
         <v>47042</v>
       </c>
@@ -20545,7 +20615,7 @@
       <c r="F1235" s="6"/>
       <c r="G1235" s="4"/>
     </row>
-    <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1236" s="10">
         <v>47043</v>
       </c>
@@ -20560,7 +20630,7 @@
       <c r="F1236" s="6"/>
       <c r="G1236" s="4"/>
     </row>
-    <row r="1237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1237" s="10">
         <v>47044</v>
       </c>
@@ -20575,7 +20645,7 @@
       <c r="F1237" s="6"/>
       <c r="G1237" s="4"/>
     </row>
-    <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1238" s="10">
         <v>47045</v>
       </c>
@@ -20590,7 +20660,7 @@
       <c r="F1238" s="7"/>
       <c r="G1238" s="5"/>
     </row>
-    <row r="1239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1239" s="10">
         <v>47046</v>
       </c>
@@ -20611,7 +20681,7 @@
       </c>
       <c r="G1239" s="3"/>
     </row>
-    <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1240" s="10">
         <v>47047</v>
       </c>
@@ -20628,7 +20698,7 @@
       <c r="F1240" s="6"/>
       <c r="G1240" s="4"/>
     </row>
-    <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1241" s="10">
         <v>47048</v>
       </c>
@@ -20643,7 +20713,7 @@
       <c r="F1241" s="6"/>
       <c r="G1241" s="4"/>
     </row>
-    <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1242" s="10">
         <v>47049</v>
       </c>
@@ -20657,8 +20727,11 @@
       <c r="E1242" s="4"/>
       <c r="F1242" s="6"/>
       <c r="G1242" s="4"/>
-    </row>
-    <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1242" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1243" s="10">
         <v>47050</v>
       </c>
@@ -20672,8 +20745,11 @@
       <c r="E1243" s="5"/>
       <c r="F1243" s="6"/>
       <c r="G1243" s="4"/>
-    </row>
-    <row r="1244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1243" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1244" s="10">
         <v>47051</v>
       </c>
@@ -20689,8 +20765,11 @@
       <c r="E1244" s="3"/>
       <c r="F1244" s="6"/>
       <c r="G1244" s="4"/>
-    </row>
-    <row r="1245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1244" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1245" s="10">
         <v>47052</v>
       </c>
@@ -20708,8 +20787,11 @@
       </c>
       <c r="F1245" s="6"/>
       <c r="G1245" s="4"/>
-    </row>
-    <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1245" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1246" s="10">
         <v>47053</v>
       </c>
@@ -20728,8 +20810,11 @@
       <c r="H1246" s="23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1246" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1247" s="10">
         <v>47054</v>
       </c>
@@ -20743,8 +20828,11 @@
       <c r="E1247" s="4"/>
       <c r="F1247" s="6"/>
       <c r="G1247" s="4"/>
-    </row>
-    <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1247" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1248" s="10">
         <v>47055</v>
       </c>
@@ -20758,8 +20846,11 @@
       <c r="E1248" s="4"/>
       <c r="F1248" s="6"/>
       <c r="G1248" s="4"/>
-    </row>
-    <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1248" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1249" s="10">
         <v>47056</v>
       </c>
@@ -20773,8 +20864,11 @@
       <c r="E1249" s="4"/>
       <c r="F1249" s="6"/>
       <c r="G1249" s="4"/>
-    </row>
-    <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1249" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1250" s="10">
         <v>47057</v>
       </c>
@@ -20788,8 +20882,11 @@
       <c r="E1250" s="4"/>
       <c r="F1250" s="6"/>
       <c r="G1250" s="4"/>
-    </row>
-    <row r="1251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1250" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1251" s="10">
         <v>47058</v>
       </c>
@@ -20807,8 +20904,11 @@
       </c>
       <c r="F1251" s="6"/>
       <c r="G1251" s="4"/>
-    </row>
-    <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1251" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1252" s="10">
         <v>47059</v>
       </c>
@@ -20825,7 +20925,7 @@
       <c r="F1252" s="6"/>
       <c r="G1252" s="4"/>
     </row>
-    <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1253" s="10">
         <v>47060</v>
       </c>
@@ -20840,7 +20940,7 @@
       <c r="F1253" s="6"/>
       <c r="G1253" s="4"/>
     </row>
-    <row r="1254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1254" s="10">
         <v>47061</v>
       </c>
@@ -20857,7 +20957,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="1255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1255" s="10">
         <v>47062</v>
       </c>
@@ -20872,7 +20972,7 @@
       <c r="F1255" s="6"/>
       <c r="G1255" s="4"/>
     </row>
-    <row r="1256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1256" s="10">
         <v>47063</v>
       </c>
@@ -20889,7 +20989,7 @@
       <c r="F1256" s="6"/>
       <c r="G1256" s="4"/>
     </row>
-    <row r="1257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1257" s="10">
         <v>47064</v>
       </c>
@@ -20908,7 +21008,7 @@
       <c r="F1257" s="6"/>
       <c r="G1257" s="4"/>
     </row>
-    <row r="1258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1258" s="10">
         <v>47065</v>
       </c>
@@ -20925,7 +21025,7 @@
       <c r="F1258" s="6"/>
       <c r="G1258" s="4"/>
     </row>
-    <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1259" s="10">
         <v>47066</v>
       </c>
@@ -20943,7 +21043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1260" s="10">
         <v>47067</v>
       </c>
@@ -20958,7 +21058,7 @@
       <c r="F1260" s="6"/>
       <c r="G1260" s="4"/>
     </row>
-    <row r="1261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1261" s="10">
         <v>47068</v>
       </c>
@@ -20973,7 +21073,7 @@
       <c r="F1261" s="6"/>
       <c r="G1261" s="4"/>
     </row>
-    <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1262" s="10">
         <v>47069</v>
       </c>
@@ -20988,7 +21088,7 @@
       <c r="F1262" s="7"/>
       <c r="G1262" s="5"/>
     </row>
-    <row r="1263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1263" s="10">
         <v>47070</v>
       </c>
@@ -21009,7 +21109,7 @@
       </c>
       <c r="G1263" s="3"/>
     </row>
-    <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1264" s="10">
         <v>47071</v>
       </c>
@@ -26592,7 +26692,7 @@
       <c r="F1600" s="6"/>
       <c r="G1600" s="4"/>
     </row>
-    <row r="1601" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1601" s="10">
         <v>47408</v>
       </c>
@@ -26607,7 +26707,7 @@
       <c r="F1601" s="6"/>
       <c r="G1601" s="4"/>
     </row>
-    <row r="1602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1602" s="10">
         <v>47409</v>
       </c>
@@ -26622,7 +26722,7 @@
       <c r="F1602" s="6"/>
       <c r="G1602" s="4"/>
     </row>
-    <row r="1603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1603" s="10">
         <v>47410</v>
       </c>
@@ -26637,7 +26737,7 @@
       <c r="F1603" s="6"/>
       <c r="G1603" s="4"/>
     </row>
-    <row r="1604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1604" s="10">
         <v>47411</v>
       </c>
@@ -26654,7 +26754,7 @@
       <c r="F1604" s="6"/>
       <c r="G1604" s="4"/>
     </row>
-    <row r="1605" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1605" s="10">
         <v>47412</v>
       </c>
@@ -26673,7 +26773,7 @@
       <c r="F1605" s="6"/>
       <c r="G1605" s="4"/>
     </row>
-    <row r="1606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1606" s="10">
         <v>47413</v>
       </c>
@@ -26690,7 +26790,7 @@
       <c r="F1606" s="6"/>
       <c r="G1606" s="4"/>
     </row>
-    <row r="1607" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1607" s="10">
         <v>47414</v>
       </c>
@@ -26704,8 +26804,11 @@
       <c r="E1607" s="4"/>
       <c r="F1607" s="6"/>
       <c r="G1607" s="4"/>
-    </row>
-    <row r="1608" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1607" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1608" s="10">
         <v>47415</v>
       </c>
@@ -26719,8 +26822,11 @@
       <c r="E1608" s="4"/>
       <c r="F1608" s="6"/>
       <c r="G1608" s="4"/>
-    </row>
-    <row r="1609" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1608" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1609" s="10">
         <v>47416</v>
       </c>
@@ -26734,8 +26840,11 @@
       <c r="E1609" s="4"/>
       <c r="F1609" s="6"/>
       <c r="G1609" s="4"/>
-    </row>
-    <row r="1610" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1609" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1610" s="10">
         <v>47417</v>
       </c>
@@ -26752,8 +26861,11 @@
       <c r="H1610" s="23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="1611" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1610" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1611" s="10">
         <v>47418</v>
       </c>
@@ -26771,8 +26883,11 @@
       </c>
       <c r="F1611" s="6"/>
       <c r="G1611" s="4"/>
-    </row>
-    <row r="1612" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1611" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1612" s="10">
         <v>47419</v>
       </c>
@@ -26788,8 +26903,11 @@
       <c r="E1612" s="4"/>
       <c r="F1612" s="6"/>
       <c r="G1612" s="4"/>
-    </row>
-    <row r="1613" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1612" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1613" s="10">
         <v>47420</v>
       </c>
@@ -26803,8 +26921,11 @@
       <c r="E1613" s="4"/>
       <c r="F1613" s="6"/>
       <c r="G1613" s="4"/>
-    </row>
-    <row r="1614" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1613" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1614" s="10">
         <v>47421</v>
       </c>
@@ -26820,8 +26941,11 @@
       <c r="G1614" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="1615" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1614" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1615" s="10">
         <v>47422</v>
       </c>
@@ -26835,8 +26959,11 @@
       <c r="E1615" s="4"/>
       <c r="F1615" s="6"/>
       <c r="G1615" s="4"/>
-    </row>
-    <row r="1616" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1615" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1616" s="10">
         <v>47423</v>
       </c>
@@ -26852,6 +26979,9 @@
       <c r="E1616" s="4"/>
       <c r="F1616" s="6"/>
       <c r="G1616" s="4"/>
+      <c r="I1616" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="1617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1617" s="10">
@@ -32684,7 +32814,7 @@
       <c r="F1968" s="6"/>
       <c r="G1968" s="4"/>
     </row>
-    <row r="1969" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1969" s="10">
         <v>47776</v>
       </c>
@@ -32699,7 +32829,7 @@
       <c r="F1969" s="6"/>
       <c r="G1969" s="4"/>
     </row>
-    <row r="1970" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1970" s="10">
         <v>47777</v>
       </c>
@@ -32714,7 +32844,7 @@
       <c r="F1970" s="6"/>
       <c r="G1970" s="4"/>
     </row>
-    <row r="1971" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1971" s="10">
         <v>47778</v>
       </c>
@@ -32733,7 +32863,7 @@
       <c r="F1971" s="6"/>
       <c r="G1971" s="4"/>
     </row>
-    <row r="1972" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1972" s="10">
         <v>47779</v>
       </c>
@@ -32749,8 +32879,11 @@
       <c r="E1972" s="4"/>
       <c r="F1972" s="6"/>
       <c r="G1972" s="4"/>
-    </row>
-    <row r="1973" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1972" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1973" s="10">
         <v>47780</v>
       </c>
@@ -32764,8 +32897,11 @@
       <c r="E1973" s="4"/>
       <c r="F1973" s="6"/>
       <c r="G1973" s="4"/>
-    </row>
-    <row r="1974" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1973" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1974" s="10">
         <v>47781</v>
       </c>
@@ -32784,8 +32920,11 @@
       <c r="H1974" s="23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="1975" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1974" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1975" s="10">
         <v>47782</v>
       </c>
@@ -32799,8 +32938,11 @@
       <c r="E1975" s="4"/>
       <c r="F1975" s="6"/>
       <c r="G1975" s="4"/>
-    </row>
-    <row r="1976" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1975" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1976" s="10">
         <v>47783</v>
       </c>
@@ -32816,8 +32958,11 @@
       <c r="E1976" s="4"/>
       <c r="F1976" s="6"/>
       <c r="G1976" s="4"/>
-    </row>
-    <row r="1977" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1976" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1977" s="10">
         <v>47784</v>
       </c>
@@ -32835,8 +32980,11 @@
       </c>
       <c r="F1977" s="6"/>
       <c r="G1977" s="4"/>
-    </row>
-    <row r="1978" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1977" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1978" s="10">
         <v>47785</v>
       </c>
@@ -32852,8 +33000,11 @@
       </c>
       <c r="F1978" s="6"/>
       <c r="G1978" s="4"/>
-    </row>
-    <row r="1979" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1978" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1979" s="10">
         <v>47786</v>
       </c>
@@ -32867,8 +33018,11 @@
       <c r="E1979" s="4"/>
       <c r="F1979" s="6"/>
       <c r="G1979" s="4"/>
-    </row>
-    <row r="1980" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1979" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1980" s="10">
         <v>47787</v>
       </c>
@@ -32882,8 +33036,11 @@
       <c r="E1980" s="4"/>
       <c r="F1980" s="6"/>
       <c r="G1980" s="4"/>
-    </row>
-    <row r="1981" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1980" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1981" s="10">
         <v>47788</v>
       </c>
@@ -32897,8 +33054,11 @@
       <c r="E1981" s="4"/>
       <c r="F1981" s="6"/>
       <c r="G1981" s="4"/>
-    </row>
-    <row r="1982" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1981" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1982" s="10">
         <v>47789</v>
       </c>
@@ -32913,7 +33073,7 @@
       <c r="F1982" s="7"/>
       <c r="G1982" s="5"/>
     </row>
-    <row r="1983" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1983" s="10">
         <v>47790</v>
       </c>
@@ -32934,7 +33094,7 @@
       </c>
       <c r="G1983" s="3"/>
     </row>
-    <row r="1984" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1984" s="10">
         <v>47791</v>
       </c>

--- a/data/events-tb.xlsx
+++ b/data/events-tb.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F1552C-990F-4CC4-9921-C622FC52709F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="2565" windowWidth="24390" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2625" yWindow="2370" windowWidth="24390" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/events-tb.xlsx
+++ b/data/events-tb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\therules\therules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F1552C-990F-4CC4-9921-C622FC52709F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305AABF5-C8F7-4EE6-8D35-63FE52B7CDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2625" yWindow="2370" windowWidth="24390" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/events-tb.xlsx
+++ b/data/events-tb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\therules\therules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305AABF5-C8F7-4EE6-8D35-63FE52B7CDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB2F206-E01C-4846-9F52-E22304ABB695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="2370" windowWidth="24390" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31740" yWindow="1560" windowWidth="24390" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5650" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5649" uniqueCount="32">
   <si>
     <t>Ruthless Slaughter</t>
   </si>
@@ -8464,9 +8464,7 @@
       <c r="E518" s="4"/>
       <c r="F518" s="7"/>
       <c r="G518" s="5"/>
-      <c r="H518" s="23" t="s">
-        <v>24</v>
-      </c>
+      <c r="H518" s="23"/>
       <c r="I518" t="s">
         <v>29</v>
       </c>
